--- a/도면_정답지.xlsx
+++ b/도면_정답지.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lang0\projects\construction-ai-estimator\reference_materials\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lang0\projects\construction-ai-estimator\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32EA65B6-2BD1-4DF8-B8B2-14DFF16522A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="도면1-기둥" sheetId="1" r:id="rId1"/>
@@ -2798,7 +2798,7 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4">
-        <f>SUM(C2:Q2)</f>
+        <f t="shared" ref="R2:R18" si="0">SUM(C2:Q2)</f>
         <v>0</v>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4">
-        <f>SUM(C3:Q3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4">
-        <f>SUM(C4:Q4)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4">
-        <f>SUM(C5:Q5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4">
-        <f>SUM(C6:Q6)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4">
-        <f>SUM(C7:Q7)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4">
-        <f>SUM(C8:Q8)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4">
-        <f>SUM(C9:Q9)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4">
-        <f>SUM(C10:Q10)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4">
-        <f>SUM(C11:Q11)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4">
-        <f>SUM(C12:Q12)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="4">
-        <f>SUM(C13:Q13)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4">
-        <f>SUM(C14:Q14)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
         <v>12</v>
       </c>
       <c r="R15" s="4">
-        <f>SUM(C15:Q15)</f>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Q16" s="4"/>
       <c r="R16" s="4">
-        <f>SUM(C16:Q16)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="Q17" s="4"/>
       <c r="R17" s="4">
-        <f>SUM(C17:Q17)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
@@ -3255,67 +3255,67 @@
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="7">
-        <f t="shared" ref="C18:Q18" si="0">SUM(C2:C17)</f>
+        <f t="shared" ref="C18:Q18" si="1">SUM(C2:C17)</f>
         <v>16</v>
       </c>
       <c r="D18" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="E18" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="F18" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="G18" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="H18" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="I18" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="K18" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L18" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="M18" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="N18" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="O18" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="P18" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="Q18" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="R18" s="7">
-        <f>SUM(C18:Q18)</f>
+        <f t="shared" si="0"/>
         <v>171</v>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4">
-        <f>SUM(C2:S2)</f>
+        <f t="shared" ref="T2:T8" si="0">SUM(C2:S2)</f>
         <v>0</v>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4">
-        <f>SUM(C3:S3)</f>
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
     </row>
@@ -4003,7 +4003,7 @@
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4">
-        <f>SUM(C4:S4)</f>
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
         <v>10</v>
       </c>
       <c r="T5" s="4">
-        <f>SUM(C5:S5)</f>
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
     </row>
@@ -4069,7 +4069,7 @@
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="4">
-        <f>SUM(C6:S6)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
       <c r="T7" s="4">
-        <f>SUM(C7:S7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4108,75 +4108,75 @@
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="7">
-        <f t="shared" ref="C8:S8" si="0">SUM(C2:C7)</f>
+        <f t="shared" ref="C8:S8" si="1">SUM(C2:C7)</f>
         <v>18</v>
       </c>
       <c r="D8" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="E8" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="F8" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="G8" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="H8" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="I8" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="J8" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="K8" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="L8" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="M8" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="N8" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="O8" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="P8" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="Q8" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="R8" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="S8" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="T8" s="7">
-        <f>SUM(C8:S8)</f>
+        <f t="shared" si="0"/>
         <v>241</v>
       </c>
     </row>
